--- a/dados/perfis/engenharia_computacao_2026_1/matriz_curricular.xlsx
+++ b/dados/perfis/engenharia_computacao_2026_1/matriz_curricular.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P161"/>
+  <dimension ref="A1:P160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,13 +595,11 @@
       <c r="L2" t="n">
         <v>60</v>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>FAGEN39401 Empreendorismo e Inovação</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -651,9 +649,6 @@
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -695,13 +690,11 @@
       <c r="L4" t="n">
         <v>60</v>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>FEELT!ED Estrutura de Dados</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -743,13 +736,11 @@
       <c r="L5" t="n">
         <v>60</v>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>FEELT!AA Análise de Algoritmos</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -799,13 +790,11 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>Inventivo|Meticuloso|Orientado por Propósito</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -855,9 +844,6 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -907,9 +893,6 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -951,13 +934,11 @@
       <c r="L9" t="n">
         <v>60</v>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>FEELT31724 Redes de Comunicações I</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -999,13 +980,11 @@
       <c r="L10" t="n">
         <v>60</v>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>FEELT31831 Redes de Comunicações II</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1055,13 +1034,11 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>Meticuloso|Adaptável|Inventivo</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1111,14 +1088,11 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FEELT!PP</t>
+          <t>FEELT!APROG2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1163,9 +1137,6 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1200,9 +1171,6 @@
           <t>COMPLEMENTAR</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1237,9 +1205,6 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1289,9 +1254,6 @@
           <t>HUMANISTICO</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1341,9 +1303,6 @@
           <t>HUMANISTICO</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1393,9 +1352,6 @@
           <t>HUMANISTICO</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1445,9 +1401,6 @@
           <t>HUMANISTICO</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1497,9 +1450,6 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1541,9 +1491,6 @@
       <c r="L21" t="n">
         <v>60</v>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1593,9 +1540,6 @@
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1645,9 +1589,6 @@
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1697,9 +1638,6 @@
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1749,9 +1687,6 @@
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1793,9 +1728,6 @@
       <c r="L26" t="n">
         <v>60</v>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1837,9 +1769,6 @@
       <c r="L27" t="n">
         <v>60</v>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1881,13 +1810,11 @@
       <c r="L28" t="n">
         <v>60</v>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>IERI39601 Engenharia Econômica</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1929,13 +1856,11 @@
       <c r="L29" t="n">
         <v>60</v>
       </c>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>IERI39601 Engenharia Econômica</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1977,9 +1902,6 @@
       <c r="L30" t="n">
         <v>60</v>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2021,9 +1943,6 @@
       <c r="L31" t="n">
         <v>60</v>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2065,9 +1984,6 @@
       <c r="L32" t="n">
         <v>30</v>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2117,9 +2033,6 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2169,9 +2082,6 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2213,9 +2123,6 @@
       <c r="L35" t="n">
         <v>45</v>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2257,9 +2164,6 @@
       <c r="L36" t="n">
         <v>60</v>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2309,9 +2213,6 @@
           <t>HUMANISTICO</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2353,9 +2254,6 @@
       <c r="L38" t="n">
         <v>45</v>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2397,9 +2295,6 @@
       <c r="L39" t="n">
         <v>60</v>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2441,9 +2336,6 @@
       <c r="L40" t="n">
         <v>60</v>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2485,9 +2377,6 @@
       <c r="L41" t="n">
         <v>45</v>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2529,9 +2418,6 @@
       <c r="L42" t="n">
         <v>45</v>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2573,9 +2459,6 @@
       <c r="L43" t="n">
         <v>60</v>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2617,9 +2500,6 @@
       <c r="L44" t="n">
         <v>45</v>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2661,9 +2541,6 @@
       <c r="L45" t="n">
         <v>60</v>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2705,9 +2582,6 @@
       <c r="L46" t="n">
         <v>60</v>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2749,9 +2623,6 @@
       <c r="L47" t="n">
         <v>45</v>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2793,9 +2664,6 @@
       <c r="L48" t="n">
         <v>45</v>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2837,9 +2705,6 @@
       <c r="L49" t="n">
         <v>30</v>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2874,9 +2739,6 @@
           <t>COMPLEMENTAR</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2926,9 +2788,6 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2978,9 +2837,6 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3030,9 +2886,6 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3074,9 +2927,6 @@
       <c r="L54" t="n">
         <v>60</v>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3118,9 +2968,6 @@
       <c r="L55" t="n">
         <v>30</v>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3170,9 +3017,6 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3222,9 +3066,6 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3274,13 +3115,11 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>Adaptável|Colaborativo|Orientado por Propósito</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3330,9 +3169,6 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3382,9 +3218,6 @@
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3434,13 +3267,11 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>Meticuloso|Inventivo|Adaptável</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3482,9 +3313,6 @@
       <c r="L62" t="n">
         <v>45</v>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3526,9 +3354,6 @@
       <c r="L63" t="n">
         <v>45</v>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3578,9 +3403,6 @@
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3630,9 +3452,6 @@
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3682,9 +3501,6 @@
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3734,9 +3550,6 @@
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3786,9 +3599,6 @@
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3838,9 +3648,6 @@
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3882,9 +3689,6 @@
       <c r="L70" t="n">
         <v>60</v>
       </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3934,9 +3738,6 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3986,9 +3787,6 @@
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4030,9 +3828,6 @@
       <c r="L73" t="n">
         <v>60</v>
       </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4074,13 +3869,11 @@
       <c r="L74" t="n">
         <v>60</v>
       </c>
-      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
           <t>FAGEN39401 Empreendorismo e Inovação</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4130,9 +3923,6 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4174,9 +3964,6 @@
       <c r="L76" t="n">
         <v>30</v>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4218,13 +4005,11 @@
       <c r="L77" t="n">
         <v>60</v>
       </c>
-      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
           <t>FEELT!FIA Fundamentos da Inteligência Artificial</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4266,13 +4051,11 @@
       <c r="L78" t="n">
         <v>60</v>
       </c>
-      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>FEELT!FIA Fundamentos da Inteligência Artificial</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4314,9 +4097,6 @@
       <c r="L79" t="n">
         <v>60</v>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4358,9 +4138,6 @@
       <c r="L80" t="n">
         <v>60</v>
       </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4410,9 +4187,6 @@
           <t>HUMANISTICO</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4454,9 +4228,6 @@
       <c r="L82" t="n">
         <v>60</v>
       </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4498,9 +4269,6 @@
       <c r="L83" t="n">
         <v>60</v>
       </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4550,9 +4318,6 @@
           <t>HUMANISTICO</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4602,9 +4367,6 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4646,9 +4408,6 @@
       <c r="L86" t="n">
         <v>60</v>
       </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4690,9 +4449,6 @@
       <c r="L87" t="n">
         <v>60</v>
       </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4734,13 +4490,11 @@
       <c r="L88" t="n">
         <v>60</v>
       </c>
-      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>FEELT!TCOMP Teoria da Computação</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4790,13 +4544,11 @@
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>Meticuloso|Adaptável|Orientado por Propósito</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4846,9 +4598,6 @@
           <t>HUMANISTICO</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4898,9 +4647,6 @@
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4950,9 +4696,6 @@
           <t>BASICO</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4994,9 +4737,6 @@
       <c r="L93" t="n">
         <v>45</v>
       </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5038,14 +4778,11 @@
       <c r="L94" t="n">
         <v>60</v>
       </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GBC212</t>
+          <t>GSI055</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5082,19 +4819,16 @@
       <c r="L95" t="n">
         <v>60</v>
       </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GSI055</t>
+          <t>GBC065</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mineração de Dados</t>
+          <t>Modelagem e Simulação</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5126,19 +4860,16 @@
       <c r="L96" t="n">
         <v>60</v>
       </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GBC065</t>
+          <t>FEELT32901</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Modelagem e Simulação</t>
+          <t>Modelagem e Simulação de Sistemas a Eventos Discretos</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5156,10 +4887,10 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -5170,19 +4901,16 @@
       <c r="L97" t="n">
         <v>60</v>
       </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FEELT32901</t>
+          <t>FEELT!MLIA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Modelagem e Simulação de Sistemas a Eventos Discretos</t>
+          <t>Modelos de Linguagem e Agentes de IA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5197,10 +4925,10 @@
         <v>0</v>
       </c>
       <c r="G98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I98" t="n">
         <v>15</v>
@@ -5212,21 +4940,18 @@
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>60</v>
-      </c>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FEELT!MLIA</t>
+          <t>GBC213</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Modelos de Linguagem e Agentes de IA</t>
+          <t>Multimídia</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5241,13 +4966,13 @@
         <v>0</v>
       </c>
       <c r="G99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I99" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -5256,21 +4981,18 @@
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>45</v>
-      </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
+        <v>60</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GBC213</t>
+          <t>FACOM32605</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Multimídia</t>
+          <t>Organização e Recuperação da Informação</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5288,10 +5010,10 @@
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -5302,19 +5024,16 @@
       <c r="L100" t="n">
         <v>60</v>
       </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FACOM32605</t>
+          <t>GSI027</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Organização e Recuperação da Informação</t>
+          <t>Otimização</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5332,10 +5051,10 @@
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I101" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -5346,14 +5065,11 @@
       <c r="L101" t="n">
         <v>60</v>
       </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GSI027</t>
+          <t>FACOM31601</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5390,19 +5106,16 @@
       <c r="L102" t="n">
         <v>60</v>
       </c>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FACOM31601</t>
+          <t>FEELT31723</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Otimização</t>
+          <t>Otimização e Simulação</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5420,10 +5133,10 @@
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -5432,21 +5145,18 @@
         <v>0</v>
       </c>
       <c r="L103" t="n">
-        <v>60</v>
-      </c>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FEELT31723</t>
+          <t>FEELT!PEC30</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Otimização e Simulação</t>
+          <t>Perspectivas em Engenharia de Computação PEC30 [por tipo]</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5458,39 +5168,24 @@
         <v>0</v>
       </c>
       <c r="F104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104" t="b">
-        <v>0</v>
-      </c>
-      <c r="H104" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" t="n">
         <v>30</v>
       </c>
-      <c r="I104" t="n">
-        <v>15</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" t="n">
-        <v>45</v>
-      </c>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FEELT!PEC30</t>
+          <t>FEELT!PEC45</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Perspectivas em Engenharia de Computação PEC30 [por tipo]</t>
+          <t>Perspectivas em Engenharia de Computação PEC45 [por tipo]</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5508,21 +5203,18 @@
         <v>1</v>
       </c>
       <c r="L105" t="n">
-        <v>30</v>
-      </c>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FEELT!PEC45</t>
+          <t>FEELT!PEC60</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Perspectivas em Engenharia de Computação PEC45 [por tipo]</t>
+          <t>Perspectivas em Engenharia de Computação PEC60 [por tipo]</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5540,21 +5232,18 @@
         <v>1</v>
       </c>
       <c r="L106" t="n">
-        <v>45</v>
-      </c>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
+        <v>60</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FEELT!PEC60</t>
+          <t>FEELT!PEC75</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Perspectivas em Engenharia de Computação PEC60 [por tipo]</t>
+          <t>Perspectivas em Engenharia de Computação PEC75 [por tipo]</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5572,21 +5261,18 @@
         <v>1</v>
       </c>
       <c r="L107" t="n">
-        <v>60</v>
-      </c>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
+        <v>75</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FEELT!PEC75</t>
+          <t>FAGEN31703</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Perspectivas em Engenharia de Computação PEC75 [por tipo]</t>
+          <t>Pesquisa Operacional</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5598,27 +5284,36 @@
         <v>0</v>
       </c>
       <c r="F108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>30</v>
+      </c>
+      <c r="I108" t="n">
+        <v>30</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>75</v>
-      </c>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
+        <v>60</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FAGEN31703</t>
+          <t>FACOM31401</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Pesquisa Operacional</t>
+          <t>Princípios e Padrões de Projeto</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5650,19 +5345,16 @@
       <c r="L109" t="n">
         <v>60</v>
       </c>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FACOM31401</t>
+          <t>GSI058</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Princípios e Padrões de Projeto</t>
+          <t>Processamento Digital de Imagens</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5680,10 +5372,10 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I110" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -5694,14 +5386,11 @@
       <c r="L110" t="n">
         <v>60</v>
       </c>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GSI058</t>
+          <t>FACOM39053</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5738,19 +5427,16 @@
       <c r="L111" t="n">
         <v>60</v>
       </c>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FACOM39053</t>
+          <t>FEELT31628</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Processamento Digital de Imagens</t>
+          <t>Processamento Digital de Sinais</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5758,20 +5444,23 @@
           <t>disciplina</t>
         </is>
       </c>
+      <c r="D112" t="n">
+        <v>6</v>
+      </c>
       <c r="E112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" t="b">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -5782,19 +5471,21 @@
       <c r="L112" t="n">
         <v>60</v>
       </c>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FEELT31628</t>
+          <t>FEELT!PF</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Processamento Digital de Sinais</t>
+          <t>Programação Funcional</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5803,7 +5494,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E113" t="b">
         <v>1</v>
@@ -5812,10 +5503,10 @@
         <v>1</v>
       </c>
       <c r="G113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I113" t="n">
         <v>15</v>
@@ -5827,21 +5518,23 @@
         <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Inventivo|Meticuloso|Autodirigido</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FEELT!PF</t>
+          <t>GBC033</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5854,23 +5547,20 @@
           <t>disciplina</t>
         </is>
       </c>
-      <c r="D114" t="n">
-        <v>3</v>
-      </c>
       <c r="E114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" t="b">
         <v>1</v>
       </c>
       <c r="G114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
         <v>30</v>
       </c>
       <c r="I114" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -5879,30 +5569,23 @@
         <v>0</v>
       </c>
       <c r="L114" t="n">
-        <v>45</v>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
+        <v>60</v>
+      </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Inventivo|Meticuloso|Autodirigido</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr"/>
+          <t>FEELT!PF Programação Funcional</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GBC033</t>
+          <t>GBC025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Programação Funcional</t>
+          <t>Programação Lógica</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5914,7 +5597,7 @@
         <v>0</v>
       </c>
       <c r="F115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G115" t="b">
         <v>0</v>
@@ -5934,23 +5617,16 @@
       <c r="L115" t="n">
         <v>60</v>
       </c>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>FEELT!PF Programação Funcional</t>
-        </is>
-      </c>
-      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GBC025</t>
+          <t>FEELT31407</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Programação Lógica</t>
+          <t>Programação Lógica e Inteligência Artificial</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5971,7 +5647,7 @@
         <v>30</v>
       </c>
       <c r="I116" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -5980,21 +5656,18 @@
         <v>0</v>
       </c>
       <c r="L116" t="n">
-        <v>60</v>
-      </c>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FEELT31407</t>
+          <t>FEELT!POO</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Programação Lógica e Inteligência Artificial</t>
+          <t>Programação Orientada a Objetos</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6002,20 +5675,23 @@
           <t>disciplina</t>
         </is>
       </c>
+      <c r="D117" t="n">
+        <v>3</v>
+      </c>
       <c r="E117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" t="n">
         <v>30</v>
       </c>
       <c r="I117" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -6024,21 +5700,23 @@
         <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>45</v>
-      </c>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FEELT!POO</t>
+          <t>FACOM32503</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Programação Orientada a Objetos</t>
+          <t>Programação para Dispositivos Móveis</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6046,17 +5724,14 @@
           <t>disciplina</t>
         </is>
       </c>
-      <c r="D118" t="n">
-        <v>3</v>
-      </c>
       <c r="E118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
         <v>30</v>
@@ -6073,24 +5748,16 @@
       <c r="L118" t="n">
         <v>60</v>
       </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FACOM32503</t>
+          <t>GBC084</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Programação para Dispositivos Móveis</t>
+          <t>Programação para Internet</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6122,19 +5789,16 @@
       <c r="L119" t="n">
         <v>60</v>
       </c>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>GBC084</t>
+          <t>GSI059</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Programação para Internet</t>
+          <t>Programação Paralela e Distribuída</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6152,10 +5816,10 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I120" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -6166,19 +5830,16 @@
       <c r="L120" t="n">
         <v>60</v>
       </c>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GSI059</t>
+          <t>FEELT!PP</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Programação Paralela e Distribuída</t>
+          <t>Programação Procedimental</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6186,20 +5847,23 @@
           <t>disciplina</t>
         </is>
       </c>
+      <c r="D121" t="n">
+        <v>2</v>
+      </c>
       <c r="E121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -6210,19 +5874,26 @@
       <c r="L121" t="n">
         <v>60</v>
       </c>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Meticuloso|Inventivo|Adaptável</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FEELT!PP</t>
+          <t>FEELT!PS</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Programação Procedimental</t>
+          <t>Programação Script</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6231,7 +5902,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" t="b">
         <v>1</v>
@@ -6262,23 +5933,21 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Meticuloso|Inventivo|Adaptável</t>
-        </is>
-      </c>
-      <c r="P122" t="inlineStr"/>
+          <t>Autodirigido|Meticuloso|Inventivo</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FEELT!PS</t>
+          <t>FEELT!PW</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Programação Script</t>
+          <t>Programação Web</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6287,13 +5956,13 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123" t="b">
         <v>1</v>
@@ -6302,7 +5971,7 @@
         <v>30</v>
       </c>
       <c r="I123" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -6311,30 +5980,23 @@
         <v>0</v>
       </c>
       <c r="L123" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr">
-        <is>
-          <t>Autodirigido|Meticuloso|Inventivo</t>
-        </is>
-      </c>
-      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FEELT!PW</t>
+          <t>GBC219</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Programação Web</t>
+          <t>Projeto de Redes de Computadores</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6342,9 +6004,6 @@
           <t>disciplina</t>
         </is>
       </c>
-      <c r="D124" t="n">
-        <v>5</v>
-      </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
@@ -6352,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="G124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I124" t="n">
         <v>15</v>
@@ -6367,26 +6026,18 @@
         <v>0</v>
       </c>
       <c r="L124" t="n">
-        <v>45</v>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
+        <v>60</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GBC219</t>
+          <t>FEELT!PHFI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Projeto de Redes de Computadores</t>
+          <t>Projetos de Hardware e Firmware para IOT</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6394,6 +6045,9 @@
           <t>disciplina</t>
         </is>
       </c>
+      <c r="D125" t="n">
+        <v>8</v>
+      </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
@@ -6401,14 +6055,14 @@
         <v>0</v>
       </c>
       <c r="G125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
         <v>45</v>
       </c>
-      <c r="I125" t="n">
-        <v>15</v>
-      </c>
       <c r="J125" t="n">
         <v>0</v>
       </c>
@@ -6416,30 +6070,29 @@
         <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>60</v>
-      </c>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FEELT!PHFI</t>
+          <t>FEELT!FPGA</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Projetos de Hardware e Firmware para IOT</t>
+          <t>Projetos Digitais com FPGA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
           <t>disciplina</t>
         </is>
-      </c>
-      <c r="D126" t="n">
-        <v>8</v>
       </c>
       <c r="E126" t="b">
         <v>0</v>
@@ -6465,24 +6118,16 @@
       <c r="L126" t="n">
         <v>45</v>
       </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FEELT!FPGA</t>
+          <t>FEELT31724</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Projetos Digitais com FPGA</t>
+          <t>Redes de Comunicações I</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6490,20 +6135,23 @@
           <t>disciplina</t>
         </is>
       </c>
+      <c r="D127" t="n">
+        <v>6</v>
+      </c>
       <c r="E127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I127" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -6512,21 +6160,23 @@
         <v>0</v>
       </c>
       <c r="L127" t="n">
-        <v>45</v>
-      </c>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FEELT31724</t>
+          <t>FEELT31831</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Redes de Comunicações I</t>
+          <t>Redes de Comunicações II</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6535,7 +6185,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E128" t="b">
         <v>1</v>
@@ -6566,19 +6216,16 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FEELT31831</t>
+          <t>FEELT39057</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Redes de Comunicações II</t>
+          <t>Redes de Sensores e Internet das Coisas</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -6586,14 +6233,11 @@
           <t>disciplina</t>
         </is>
       </c>
-      <c r="D129" t="n">
-        <v>7</v>
-      </c>
       <c r="E129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129" t="b">
         <v>0</v>
@@ -6613,24 +6257,16 @@
       <c r="L129" t="n">
         <v>60</v>
       </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FEELT39057</t>
+          <t>FEELT31713</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Redes de Sensores e Internet das Coisas</t>
+          <t>Redes Industriais para Controle e Automação I</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6642,13 +6278,13 @@
         <v>0</v>
       </c>
       <c r="F130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130" t="b">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I130" t="n">
         <v>15</v>
@@ -6660,21 +6296,23 @@
         <v>0</v>
       </c>
       <c r="L130" t="n">
-        <v>60</v>
-      </c>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>FEELT31724 Redes de Comunicações I</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FEELT31713</t>
+          <t>FEELT32801</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Redes Industriais para Controle e Automação I</t>
+          <t>Redes Industriais para Controle e Automação II</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6692,10 +6330,10 @@
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I131" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -6704,25 +6342,23 @@
         <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>75</v>
-      </c>
-      <c r="N131" t="inlineStr"/>
+        <v>90</v>
+      </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>FEELT31724 Redes de Comunicações I</t>
-        </is>
-      </c>
-      <c r="P131" t="inlineStr"/>
+          <t>FEELT31831 Redes de Comunicações II</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FEELT32801</t>
+          <t>FEELT39042</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Redes Industriais para Controle e Automação II</t>
+          <t>Resolução de Problemas</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6734,7 +6370,7 @@
         <v>0</v>
       </c>
       <c r="F132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G132" t="b">
         <v>0</v>
@@ -6743,7 +6379,7 @@
         <v>30</v>
       </c>
       <c r="I132" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -6752,25 +6388,18 @@
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>90</v>
-      </c>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>FEELT31831 Redes de Comunicações II</t>
-        </is>
-      </c>
-      <c r="P132" t="inlineStr"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FEELT39042</t>
+          <t>FEELT!RP1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Resolução de Problemas</t>
+          <t>Resolução de Problemas I</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6785,13 +6414,13 @@
         <v>0</v>
       </c>
       <c r="G133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -6802,19 +6431,16 @@
       <c r="L133" t="n">
         <v>45</v>
       </c>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FEELT!RP1</t>
+          <t>FEELT!RP2</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Resolução de Problemas I</t>
+          <t>Resolução de Problemas II</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6846,19 +6472,16 @@
       <c r="L134" t="n">
         <v>45</v>
       </c>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FEELT!RP2</t>
+          <t>FEELT31722</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Resolução de Problemas II</t>
+          <t>Robótica</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -6873,13 +6496,13 @@
         <v>0</v>
       </c>
       <c r="G135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I135" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -6888,21 +6511,18 @@
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>45</v>
-      </c>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
+        <v>60</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FEELT31722</t>
+          <t>FEELT!SEG</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Robótica</t>
+          <t>Segurança de Sistemas Computacionais</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -6910,43 +6530,48 @@
           <t>disciplina</t>
         </is>
       </c>
+      <c r="D136" t="n">
+        <v>7</v>
+      </c>
       <c r="E136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H136" t="n">
+        <v>15</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>30</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
         <v>45</v>
       </c>
-      <c r="I136" t="n">
-        <v>15</v>
-      </c>
-      <c r="J136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" t="n">
-        <v>60</v>
-      </c>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FEELT!SEG</t>
+          <t>FEELT31526</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Segurança de Sistemas Computacionais</t>
+          <t>Sinais e Multimídia</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6954,26 +6579,23 @@
           <t>disciplina</t>
         </is>
       </c>
-      <c r="D137" t="n">
-        <v>7</v>
-      </c>
       <c r="E137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
+        <v>30</v>
+      </c>
+      <c r="I137" t="n">
         <v>15</v>
       </c>
-      <c r="I137" t="n">
-        <v>0</v>
-      </c>
       <c r="J137" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -6981,24 +6603,16 @@
       <c r="L137" t="n">
         <v>45</v>
       </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FEELT31526</t>
+          <t>FEELT!SCTR</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sinais e Multimídia</t>
+          <t>Sistemas Computacionais em Tempo Real</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7006,20 +6620,23 @@
           <t>disciplina</t>
         </is>
       </c>
+      <c r="D138" t="n">
+        <v>7</v>
+      </c>
       <c r="E138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H138" t="n">
+        <v>15</v>
+      </c>
+      <c r="I138" t="n">
         <v>30</v>
-      </c>
-      <c r="I138" t="n">
-        <v>15</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -7030,19 +6647,21 @@
       <c r="L138" t="n">
         <v>45</v>
       </c>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FEELT!SCTR</t>
+          <t>GBC043</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sistemas Computacionais em Tempo Real</t>
+          <t>Sistemas de Banco de Dados</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7050,20 +6669,17 @@
           <t>disciplina</t>
         </is>
       </c>
-      <c r="D139" t="n">
-        <v>7</v>
-      </c>
       <c r="E139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F139" t="b">
         <v>1</v>
       </c>
       <c r="G139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I139" t="n">
         <v>30</v>
@@ -7075,26 +6691,23 @@
         <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>45</v>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>FEELT!BD Banco de Dados</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>GBC043</t>
+          <t>FEELT31409</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Sistemas de Banco de Dados</t>
+          <t>Sistemas Digitais</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7102,8 +6715,11 @@
           <t>disciplina</t>
         </is>
       </c>
+      <c r="D140" t="n">
+        <v>2</v>
+      </c>
       <c r="E140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" t="b">
         <v>1</v>
@@ -7112,37 +6728,35 @@
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
         <v>30</v>
       </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" t="n">
-        <v>90</v>
-      </c>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>FEELT!BD Banco de Dados</t>
-        </is>
-      </c>
-      <c r="P140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FEELT31409</t>
+          <t>FEELT31410</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Sistemas Digitais</t>
+          <t>Sistemas Digitais, Experimental de</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7163,10 +6777,10 @@
         <v>0</v>
       </c>
       <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
         <v>30</v>
-      </c>
-      <c r="I141" t="n">
-        <v>0</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -7182,19 +6796,16 @@
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FEELT31410</t>
+          <t>FEELT!SD</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Sistemas Digitais, Experimental de</t>
+          <t>Sistemas Distribuídos</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7203,7 +6814,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E142" t="b">
         <v>1</v>
@@ -7212,13 +6823,13 @@
         <v>1</v>
       </c>
       <c r="G142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I142" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -7227,21 +6838,18 @@
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FEELT!SD</t>
+          <t>GBC074</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7254,20 +6862,17 @@
           <t>disciplina</t>
         </is>
       </c>
-      <c r="D143" t="n">
-        <v>8</v>
-      </c>
       <c r="E143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F143" t="b">
         <v>1</v>
       </c>
       <c r="G143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
@@ -7279,21 +6884,18 @@
         <v>0</v>
       </c>
       <c r="L143" t="n">
-        <v>45</v>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>FEELT!SD Sistemas Distribuídos</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GBC074</t>
+          <t>FACOM32606</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -7330,23 +6932,21 @@
       <c r="L144" t="n">
         <v>60</v>
       </c>
-      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
           <t>FEELT!SD Sistemas Distribuídos</t>
         </is>
       </c>
-      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FACOM32606</t>
+          <t>FEELT!SCON</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Sistemas Distribuídos</t>
+          <t>Sistemas e Controle</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7354,20 +6954,23 @@
           <t>disciplina</t>
         </is>
       </c>
+      <c r="D145" t="n">
+        <v>7</v>
+      </c>
       <c r="E145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" t="b">
         <v>1</v>
       </c>
       <c r="G145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -7376,25 +6979,23 @@
         <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>60</v>
-      </c>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>FEELT!SD Sistemas Distribuídos</t>
-        </is>
-      </c>
-      <c r="P145" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FEELT!SCON</t>
+          <t>FEELT31523</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Sistemas e Controle</t>
+          <t>Sistemas Embarcados I</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -7403,7 +7004,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E146" t="b">
         <v>1</v>
@@ -7412,14 +7013,14 @@
         <v>1</v>
       </c>
       <c r="G146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146" t="n">
+        <v>45</v>
+      </c>
+      <c r="I146" t="n">
         <v>30</v>
       </c>
-      <c r="I146" t="n">
-        <v>15</v>
-      </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
@@ -7427,26 +7028,23 @@
         <v>0</v>
       </c>
       <c r="L146" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
           <t>TECNOLOGICO</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FEELT31523</t>
+          <t>FEELT39015</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Sistemas Embarcados I</t>
+          <t>Sistemas Embarcados II</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -7454,20 +7052,17 @@
           <t>disciplina</t>
         </is>
       </c>
-      <c r="D147" t="n">
-        <v>6</v>
-      </c>
       <c r="E147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G147" t="b">
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I147" t="n">
         <v>30</v>
@@ -7479,26 +7074,18 @@
         <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>75</v>
-      </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
+        <v>60</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FEELT39015</t>
+          <t>FEELT!SO</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Sistemas Embarcados II</t>
+          <t>Sistemas Operacionais</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -7506,20 +7093,23 @@
           <t>disciplina</t>
         </is>
       </c>
+      <c r="D148" t="n">
+        <v>5</v>
+      </c>
       <c r="E148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I148" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -7528,16 +7118,18 @@
         <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>60</v>
-      </c>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FEELT!SO</t>
+          <t>GBC045</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7550,23 +7142,20 @@
           <t>disciplina</t>
         </is>
       </c>
-      <c r="D149" t="n">
-        <v>5</v>
-      </c>
       <c r="E149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F149" t="b">
         <v>1</v>
       </c>
       <c r="G149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -7575,26 +7164,23 @@
         <v>0</v>
       </c>
       <c r="L149" t="n">
-        <v>45</v>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>FEELT!SO Sistemas Operacionais</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>GBC045</t>
+          <t>FEELT31521</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Sistemas Operacionais</t>
+          <t>Tecnologias Web e Mobile</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7606,16 +7192,16 @@
         <v>0</v>
       </c>
       <c r="F150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G150" t="b">
         <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I150" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -7624,25 +7210,18 @@
         <v>0</v>
       </c>
       <c r="L150" t="n">
-        <v>90</v>
-      </c>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>FEELT!SO Sistemas Operacionais</t>
-        </is>
-      </c>
-      <c r="P150" t="inlineStr"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FEELT31521</t>
+          <t>FEELT!TCOMP</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Tecnologias Web e Mobile</t>
+          <t>Teoria da Computação</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7650,20 +7229,23 @@
           <t>disciplina</t>
         </is>
       </c>
+      <c r="D151" t="n">
+        <v>6</v>
+      </c>
       <c r="E151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I151" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -7674,19 +7256,26 @@
       <c r="L151" t="n">
         <v>45</v>
       </c>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Meticuloso|Adaptável|Inventivo</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FEELT!TCOMP</t>
+          <t>FEELT!TEC30</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Teoria da Computação</t>
+          <t>Tópicos em Engenharia de Computação TEC30 [por tipo]</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7694,55 +7283,28 @@
           <t>disciplina</t>
         </is>
       </c>
-      <c r="D152" t="n">
-        <v>6</v>
-      </c>
       <c r="E152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G152" t="b">
         <v>1</v>
       </c>
-      <c r="H152" t="n">
-        <v>45</v>
-      </c>
-      <c r="I152" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" t="n">
-        <v>0</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0</v>
-      </c>
       <c r="L152" t="n">
-        <v>45</v>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>Meticuloso|Adaptável|Inventivo</t>
-        </is>
-      </c>
-      <c r="P152" t="inlineStr"/>
+        <v>30</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FEELT!TEC30</t>
+          <t>FEELT!TEC45</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Tópicos em Engenharia de Computação TEC30 [por tipo]</t>
+          <t>Tópicos em Engenharia de Computação TEC45 [por tipo]</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7760,21 +7322,18 @@
         <v>1</v>
       </c>
       <c r="L153" t="n">
-        <v>30</v>
-      </c>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FEELT!TEC45</t>
+          <t>FEELT!TEC60</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Tópicos em Engenharia de Computação TEC45 [por tipo]</t>
+          <t>Tópicos em Engenharia de Computação TEC60 [por tipo]</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7792,21 +7351,18 @@
         <v>1</v>
       </c>
       <c r="L154" t="n">
-        <v>45</v>
-      </c>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
+        <v>60</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FEELT!TEC60</t>
+          <t>FEELT!TEC75</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Tópicos em Engenharia de Computação TEC60 [por tipo]</t>
+          <t>Tópicos em Engenharia de Computação TEC75 [por tipo]</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7824,21 +7380,18 @@
         <v>1</v>
       </c>
       <c r="L155" t="n">
-        <v>60</v>
-      </c>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
+        <v>75</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FEELT!TEC75</t>
+          <t>FEELT39040E</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Tópicos em Engenharia de Computação TEC75 [por tipo]</t>
+          <t>Tópicos Especiais em Engenharia de Computação: Bancos de Dados Não Relacionais</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7853,24 +7406,33 @@
         <v>0</v>
       </c>
       <c r="G156" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>30</v>
+      </c>
+      <c r="I156" t="n">
+        <v>15</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>75</v>
-      </c>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FEELT39040E</t>
+          <t>FEELT39040C</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Tópicos Especiais em Engenharia de Computação: Bancos de Dados Não Relacionais</t>
+          <t>Tópicos Especiais em Engenharia de Computação: Cloud Computing Architecture AWS</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7902,19 +7464,16 @@
       <c r="L157" t="n">
         <v>45</v>
       </c>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FEELT39040C</t>
+          <t>FEELT39040G</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Tópicos Especiais em Engenharia de Computação: Cloud Computing Architecture AWS</t>
+          <t>Tópicos Especiais em Engenharia de Computação: Computação Evolutiva</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7946,19 +7505,16 @@
       <c r="L158" t="n">
         <v>45</v>
       </c>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FEELT39040G</t>
+          <t>FEELT39040P</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Tópicos Especiais em Engenharia de Computação: Computação Evolutiva</t>
+          <t>Tópicos Especiais em Engenharia de Computação: Desenvolvimento de hardware microcontrolado e firmware para IoT</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7990,19 +7546,16 @@
       <c r="L159" t="n">
         <v>45</v>
       </c>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FEELT39040P</t>
+          <t>FEELT39040F</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Tópicos Especiais em Engenharia de Computação: Desenvolvimento de hardware microcontrolado e firmware para IoT</t>
+          <t>Tópicos Especiais em Engenharia de Computação: Desenvolvimento de Jogos com uso de Realidade Virtual e Aumentada</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -8034,53 +7587,6 @@
       <c r="L160" t="n">
         <v>45</v>
       </c>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>FEELT39040F</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Tópicos Especiais em Engenharia de Computação: Desenvolvimento de Jogos com uso de Realidade Virtual e Aumentada</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>disciplina</t>
-        </is>
-      </c>
-      <c r="E161" t="b">
-        <v>0</v>
-      </c>
-      <c r="F161" t="b">
-        <v>0</v>
-      </c>
-      <c r="G161" t="b">
-        <v>0</v>
-      </c>
-      <c r="H161" t="n">
-        <v>30</v>
-      </c>
-      <c r="I161" t="n">
-        <v>15</v>
-      </c>
-      <c r="J161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" t="n">
-        <v>0</v>
-      </c>
-      <c r="L161" t="n">
-        <v>45</v>
-      </c>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8241,7 +7747,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FEELT!PP</t>
+          <t>FEELT!APROG2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -8259,7 +7765,6 @@
           <t>ACC</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="b">
         <v>0</v>
       </c>
@@ -9119,7 +8624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9737,7 +9242,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FEELT!PP</t>
+          <t>FEELT!PS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9749,31 +9254,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FEELT!PS</t>
+          <t>FEELT!PW</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CC2020_FUNDAMENTOS_SOFTWARE</t>
+          <t>CC2020_MODELAGEM_SISTEMAS</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FEELT!PW</t>
+          <t>FEELT!PHFI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CC2020_MODELAGEM_SISTEMAS</t>
+          <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FEELT!PHFI</t>
+          <t>FEELT31724</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9785,7 +9290,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FEELT31724</t>
+          <t>FEELT31831</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9797,7 +9302,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FEELT31831</t>
+          <t>FEELT!SEG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9809,7 +9314,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FEELT!SEG</t>
+          <t>FEELT!SCTR</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9821,19 +9326,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FEELT!SCTR</t>
+          <t>FEELT31409</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
+          <t>CC2020_HARDWARE</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FEELT31409</t>
+          <t>FEELT31410</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -9845,19 +9350,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FEELT31410</t>
+          <t>FEELT!SD</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CC2020_HARDWARE</t>
+          <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FEELT!SD</t>
+          <t>FEELT!SCON</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9869,7 +9374,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FEELT!SCON</t>
+          <t>FEELT31523</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9881,34 +9386,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FEELT31523</t>
+          <t>FEELT!SO</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
+          <t>CC2020_FUNDAMENTOS_SOFTWARE</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FEELT!SO</t>
+          <t>FEELT!TCOMP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
-        <is>
-          <t>CC2020_FUNDAMENTOS_SOFTWARE</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>FEELT!TCOMP</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
         <is>
           <t>CC2020_FUNDAMENTOS_SOFTWARE</t>
         </is>
@@ -10143,7 +9636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B172"/>
+  <dimension ref="A1:B171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11613,7 +11106,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FEELT!PP</t>
+          <t>FEELT!PS</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11625,24 +11118,24 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FEELT!PS</t>
+          <t>FEELT!FPGA</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DCN_BASE_33</t>
+          <t>DCN_TEC_01</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FEELT!FPGA</t>
+          <t>FEELT31724</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DCN_TEC_01</t>
+          <t>DCN_BASE_04</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11147,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DCN_BASE_04</t>
+          <t>DCN_BASE_39</t>
         </is>
       </c>
     </row>
@@ -11666,19 +11159,19 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DCN_BASE_39</t>
+          <t>DCN_TEC_04</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FEELT31724</t>
+          <t>FEELT31831</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DCN_TEC_04</t>
+          <t>DCN_BASE_04</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11183,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DCN_BASE_04</t>
+          <t>DCN_BASE_39</t>
         </is>
       </c>
     </row>
@@ -11702,31 +11195,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DCN_BASE_39</t>
+          <t>DCN_TEC_04</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FEELT31831</t>
+          <t>FEELT31722</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DCN_TEC_04</t>
+          <t>DCN_BASE_16</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FEELT31722</t>
+          <t>FEELT!SEG</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DCN_BASE_16</t>
+          <t>DCN_BASE_11</t>
         </is>
       </c>
     </row>
@@ -11738,7 +11231,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DCN_BASE_11</t>
+          <t>DCN_BASE_00</t>
         </is>
       </c>
     </row>
@@ -11750,19 +11243,19 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DCN_BASE_00</t>
+          <t>DCN_BASE_04</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FEELT!SEG</t>
+          <t>FEELT!SCTR</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DCN_BASE_04</t>
+          <t>DCN_BASE_39</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11267,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>DCN_BASE_39</t>
+          <t>DCN_BASE_10</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11279,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DCN_BASE_10</t>
+          <t>DCN_BASE_00</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11291,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DCN_BASE_00</t>
+          <t>DCN_BASE_05</t>
         </is>
       </c>
     </row>
@@ -11810,7 +11303,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DCN_BASE_05</t>
+          <t>DCN_TEC_05</t>
         </is>
       </c>
     </row>
@@ -11822,7 +11315,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>DCN_TEC_05</t>
+          <t>DCN_TEC_00</t>
         </is>
       </c>
     </row>
@@ -11834,19 +11327,19 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DCN_TEC_00</t>
+          <t>DCN_TEC_06</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FEELT!SCTR</t>
+          <t>FEELT31409</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DCN_TEC_06</t>
+          <t>DCN_BASE_37</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11351,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DCN_BASE_37</t>
+          <t>DCN_TEC_10</t>
         </is>
       </c>
     </row>
@@ -11870,19 +11363,19 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DCN_TEC_10</t>
+          <t>DCN_TEC_00</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FEELT31409</t>
+          <t>FEELT31410</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DCN_TEC_00</t>
+          <t>DCN_BASE_37</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11387,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DCN_BASE_37</t>
+          <t>DCN_TEC_10</t>
         </is>
       </c>
     </row>
@@ -11906,19 +11399,19 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DCN_TEC_10</t>
+          <t>DCN_TEC_00</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FEELT31410</t>
+          <t>FEELT!SD</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DCN_TEC_00</t>
+          <t>DCN_BASE_39</t>
         </is>
       </c>
     </row>
@@ -11930,7 +11423,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DCN_BASE_39</t>
+          <t>DCN_BASE_09</t>
         </is>
       </c>
     </row>
@@ -11942,7 +11435,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DCN_BASE_09</t>
+          <t>DCN_BASE_10</t>
         </is>
       </c>
     </row>
@@ -11954,7 +11447,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DCN_BASE_10</t>
+          <t>DCN_BASE_15</t>
         </is>
       </c>
     </row>
@@ -11966,19 +11459,19 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DCN_BASE_15</t>
+          <t>DCN_TEC_04</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FEELT!SD</t>
+          <t>FEELT!SCON</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DCN_TEC_04</t>
+          <t>DCN_BASE_18</t>
         </is>
       </c>
     </row>
@@ -11990,7 +11483,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DCN_BASE_18</t>
+          <t>DCN_BASE_34</t>
         </is>
       </c>
     </row>
@@ -12002,7 +11495,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>DCN_BASE_34</t>
+          <t>DCN_TEC_05</t>
         </is>
       </c>
     </row>
@@ -12014,19 +11507,19 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DCN_TEC_05</t>
+          <t>DCN_TEC_06</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FEELT!SCON</t>
+          <t>FEELT31523</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DCN_TEC_06</t>
+          <t>DCN_BASE_18</t>
         </is>
       </c>
     </row>
@@ -12038,7 +11531,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DCN_BASE_18</t>
+          <t>DCN_BASE_00</t>
         </is>
       </c>
     </row>
@@ -12050,7 +11543,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DCN_BASE_00</t>
+          <t>DCN_BASE_05</t>
         </is>
       </c>
     </row>
@@ -12062,7 +11555,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>DCN_BASE_05</t>
+          <t>DCN_BASE_13</t>
         </is>
       </c>
     </row>
@@ -12074,7 +11567,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DCN_BASE_13</t>
+          <t>DCN_TEC_00</t>
         </is>
       </c>
     </row>
@@ -12086,7 +11579,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>DCN_TEC_00</t>
+          <t>DCN_TEC_10</t>
         </is>
       </c>
     </row>
@@ -12098,7 +11591,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DCN_TEC_10</t>
+          <t>DCN_TEC_02</t>
         </is>
       </c>
     </row>
@@ -12110,7 +11603,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DCN_TEC_02</t>
+          <t>DCN_TEC_07</t>
         </is>
       </c>
     </row>
@@ -12122,7 +11615,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DCN_TEC_07</t>
+          <t>DCN_TEC_05</t>
         </is>
       </c>
     </row>
@@ -12134,31 +11627,31 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DCN_TEC_05</t>
+          <t>DCN_TEC_06</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FEELT31523</t>
+          <t>FEELT!SO</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>DCN_TEC_06</t>
+          <t>DCN_BASE_00</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FEELT!SO</t>
+          <t>FEELT!TCOMP</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>DCN_BASE_00</t>
+          <t>DCN_BASE_27</t>
         </is>
       </c>
     </row>
@@ -12170,7 +11663,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>DCN_BASE_27</t>
+          <t>DCN_BASE_30</t>
         </is>
       </c>
     </row>
@@ -12182,7 +11675,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DCN_BASE_30</t>
+          <t>DCN_BASE_29</t>
         </is>
       </c>
     </row>
@@ -12193,18 +11686,6 @@
         </is>
       </c>
       <c r="B171" t="inlineStr">
-        <is>
-          <t>DCN_BASE_29</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>FEELT!TCOMP</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
         <is>
           <t>DCN_BASE_35</t>
         </is>
